--- a/SGC-CKN/Excel/a9665892-b9f8-481b-aad4-7578f8936247_Đại_trà_P1-60_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/a9665892-b9f8-481b-aad4-7578f8936247_Đại_trà_P1-60_D800_28-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,7 +106,7 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 1.8 - 0.71 = 1.09</t>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -119,9 +119,6 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 4.7 - 1.8 = 2.9</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 8.5 - 4.7 = 3.8</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -145,9 +139,6 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 17.2 - 8.5 = 8.7</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -158,9 +149,6 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 22.5 - 17.2 = 5.3</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -171,9 +159,6 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 26.8 - 22.5 = 4.3</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -184,9 +169,6 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tự tính: 39.3 - 26.8 = 12.5</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -197,7 +179,7 @@
 28/03/2026</t>
   </si>
   <si>
-    <t>Chạm sỏi tại 39.3m. Độ sâu cuối cùng 44.38m. Cao độ thiết kế -35.42m.</t>
+    <t>Chạm sỏi tại 39.3m. C ĐS -35.42m.</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -228,9 +210,6 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -1169,7 +1148,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.8</v>
@@ -1178,10 +1157,10 @@
         <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="J11" s="8">
-        <v>6.54</v>
+        <v>10.8</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1219,24 +1198,24 @@
         <v>8.7</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-4.7</v>
@@ -1254,24 +1233,24 @@
         <v>11.4</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14" s="15">
         <v>-8.5</v>
@@ -1289,24 +1268,24 @@
         <v>17.4</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F15" s="18">
         <v>-17.2</v>
@@ -1324,24 +1303,24 @@
         <v>15.9</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D16" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>45</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="F16" s="21">
         <v>-22.5</v>
@@ -1359,24 +1338,24 @@
         <v>5.16</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F17" s="24">
         <v>-26.8</v>
@@ -1394,24 +1373,24 @@
         <v>3.91</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F18" s="28">
         <v>-39.3</v>
@@ -1429,12 +1408,12 @@
         <v>3.91</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1540,31 +1519,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1581,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.8</v>
@@ -1590,10 +1569,10 @@
         <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="I2" s="8">
-        <v>6.54</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1633,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1662,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1691,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1720,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
@@ -1749,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -1778,7 +1757,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1801,19 +1780,19 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.38</v>
@@ -1822,10 +1801,10 @@
         <v>7</v>
       </c>
       <c r="H10" s="33">
-        <v>43.67</v>
+        <v>44.38</v>
       </c>
       <c r="I10" s="33">
-        <v>6.24</v>
+        <v>6.34</v>
       </c>
     </row>
   </sheetData>
